--- a/Config/UnlockConditionConfig.xlsx
+++ b/Config/UnlockConditionConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11850" windowHeight="11805"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -115,10 +115,7 @@
     <t>TwoThreeFive</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>亮出5次散牌235后解锁</t>
+    <t>亮出1次散牌235并且击败1次豹子牌型解锁</t>
   </si>
   <si>
     <t>ShuffleCardAndVictory</t>
@@ -755,14 +752,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1190,7 +1184,7 @@
     </row>
     <row r="5" customFormat="1" spans="1:6">
       <c r="A5" s="1"/>
-      <c r="B5" s="3">
+      <c r="B5" s="2">
         <v>1001</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1207,7 +1201,7 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="B6" s="3">
+      <c r="B6" s="2">
         <v>1002</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -1224,7 +1218,7 @@
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="B7" s="3">
+      <c r="B7" s="2">
         <v>1003</v>
       </c>
       <c r="C7" s="2" t="s">
@@ -1241,7 +1235,7 @@
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>1004</v>
       </c>
       <c r="C8" s="2" t="s">
@@ -1258,7 +1252,7 @@
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="B9" s="3">
+      <c r="B9" s="2">
         <v>1005</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -1268,18 +1262,18 @@
         <v>17</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
         <v>27</v>
-      </c>
-      <c r="F9" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="B10" s="3">
+      <c r="B10" s="2">
         <v>1006</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>17</v>
@@ -1288,11 +1282,11 @@
         <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="B11" s="3">
+      <c r="B11" s="2">
         <v>1007</v>
       </c>
       <c r="C11" s="2" t="s">
@@ -1302,27 +1296,27 @@
         <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" t="s">
         <v>31</v>
-      </c>
-      <c r="F11" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="B12" s="3">
+      <c r="B12" s="2">
         <v>1008</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/Config/UnlockConditionConfig.xlsx
+++ b/Config/UnlockConditionConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="19995" windowHeight="11520"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -137,6 +137,54 @@
   </si>
   <si>
     <t>亮出50次数字牌7后解锁</t>
+  </si>
+  <si>
+    <t>Flush</t>
+  </si>
+  <si>
+    <t>亮出20次同花后解锁</t>
+  </si>
+  <si>
+    <t>AccumulateGold</t>
+  </si>
+  <si>
+    <t>累计获得2000金币后解锁</t>
+  </si>
+  <si>
+    <t>刷新40次商店后解锁</t>
+  </si>
+  <si>
+    <t>击杀150只敌人后解锁</t>
+  </si>
+  <si>
+    <t>亮出35次同花后解锁</t>
+  </si>
+  <si>
+    <t>使用搓牌并战胜200次敌人后解锁</t>
+  </si>
+  <si>
+    <t>亮出60次同花后解锁</t>
+  </si>
+  <si>
+    <t>SingleDamage</t>
+  </si>
+  <si>
+    <t>单次比牌造成300点伤害后解锁</t>
+  </si>
+  <si>
+    <t>亮出60次顺子后解锁</t>
+  </si>
+  <si>
+    <t>使用300次搓牌后解锁</t>
+  </si>
+  <si>
+    <t>ClearDifficulty</t>
+  </si>
+  <si>
+    <t>通关难度3后解锁</t>
+  </si>
+  <si>
+    <t>累计获得5000金币后解锁</t>
   </si>
 </sst>
 </file>
@@ -302,12 +350,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -607,160 +661,169 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1110,214 +1173,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.75833333333333" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.86666666666667" style="1" customWidth="1"/>
-    <col min="3" max="3" width="13.3666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="10.2166666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.4083333333333" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="5.75833333333333" style="2" customWidth="1"/>
+    <col min="2" max="2" width="5.86666666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.3666666666667" style="3" customWidth="1"/>
+    <col min="4" max="4" width="10.2166666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6.375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="21.4083333333333" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="1:6">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2">
+    <row r="5" spans="1:7">
+      <c r="B5" s="3">
         <v>1001</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>1</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <v>40</v>
       </c>
       <c r="F5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="B6" s="2">
+    <row r="6" spans="1:7">
+      <c r="B6" s="3">
         <v>1002</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="B7" s="2">
+    <row r="7" spans="1:7">
+      <c r="B7" s="3">
         <v>1003</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="B8" s="2">
+    <row r="8" spans="1:7">
+      <c r="B8" s="3">
         <v>1004</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="F8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="B9" s="2">
+    <row r="9" spans="1:7">
+      <c r="B9" s="3">
         <v>1005</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F9" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="B10" s="2">
+    <row r="10" spans="1:7">
+      <c r="B10" s="3">
         <v>1006</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
-      <c r="B11" s="2">
+    <row r="11" spans="1:7">
+      <c r="B11" s="3">
         <v>1007</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="B12" s="2">
+    <row r="12" spans="1:7">
+      <c r="B12" s="3">
         <v>1008</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>34</v>
       </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:7">
+      <c r="B13" s="4">
+        <v>1009</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>20</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:7">
+      <c r="B14" s="4">
+        <v>1010</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2000</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:7">
+      <c r="B15" s="4">
+        <v>1011</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>40</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:7">
+      <c r="B16" s="4">
+        <v>1012</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>150</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="2:7">
+      <c r="B17" s="4">
+        <v>1013</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>35</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="2:7">
+      <c r="B18" s="4">
+        <v>1014</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>200</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="2:7">
+      <c r="B19" s="4">
+        <v>1015</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4">
+        <v>60</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="2:7">
+      <c r="B20" s="4">
+        <v>1016</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4">
+        <v>300</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="2:7">
+      <c r="B21" s="4">
+        <v>1017</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4">
+        <v>60</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="2:7">
+      <c r="B22" s="4">
+        <v>1018</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4">
+        <v>300</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="2:7">
+      <c r="B23" s="4">
+        <v>1019</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4">
+        <v>3</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="2:7">
+      <c r="B24" s="4">
+        <v>1020</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4">
+        <v>5000</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/UnlockConditionConfig.xlsx
+++ b/Config/UnlockConditionConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19995" windowHeight="11520"/>
+    <workbookView windowWidth="14175" windowHeight="11520"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -1482,7 +1482,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="4">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>42</v>

--- a/Config/UnlockConditionConfig.xlsx
+++ b/Config/UnlockConditionConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14175" windowHeight="11520"/>
+    <workbookView windowWidth="13170" windowHeight="10470"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="83">
   <si>
     <t>##var</t>
   </si>
@@ -76,115 +76,211 @@
     <t>描述</t>
   </si>
   <si>
+    <t>10101</t>
+  </si>
+  <si>
+    <t>Couplet</t>
+  </si>
+  <si>
+    <t>亮出20次对子后解锁</t>
+  </si>
+  <si>
+    <t>10201</t>
+  </si>
+  <si>
+    <t>Flush</t>
+  </si>
+  <si>
+    <t>亮出20次同花后解锁</t>
+  </si>
+  <si>
+    <t>10301</t>
+  </si>
+  <si>
+    <t>Straight</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>亮出20次顺子后解锁</t>
+  </si>
+  <si>
+    <t>10401</t>
+  </si>
+  <si>
     <t>KillMonster</t>
   </si>
   <si>
+    <t>击杀20只敌人后解锁</t>
+  </si>
+  <si>
+    <t>10402</t>
+  </si>
+  <si>
     <t>击杀40只敌人后解锁</t>
   </si>
   <si>
+    <t>10501</t>
+  </si>
+  <si>
+    <t>ClearDifficulty</t>
+  </si>
+  <si>
+    <t>首次通关难度2解锁</t>
+  </si>
+  <si>
+    <t>10502</t>
+  </si>
+  <si>
+    <t>首次通关难度3解锁</t>
+  </si>
+  <si>
+    <t>10601</t>
+  </si>
+  <si>
     <t>ShuffleCard</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>使用90次搓牌后解锁</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>使用30次搓牌后解锁</t>
+  </si>
+  <si>
+    <t>10602</t>
+  </si>
+  <si>
+    <t>使用120次搓牌后解锁</t>
+  </si>
+  <si>
+    <t>10701</t>
   </si>
   <si>
     <t>RefreshStore</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>刷新25次商店后解锁</t>
-  </si>
-  <si>
-    <t>Straight</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>亮出30次顺子后解锁</t>
+    <t>刷新20次商店后解锁</t>
+  </si>
+  <si>
+    <t>10801</t>
+  </si>
+  <si>
+    <t>Failure</t>
+  </si>
+  <si>
+    <t>负于对手30次后解锁</t>
+  </si>
+  <si>
+    <t>10901</t>
+  </si>
+  <si>
+    <t>Defeat</t>
+  </si>
+  <si>
+    <t>战胜对手30次后解锁</t>
+  </si>
+  <si>
+    <t>11001</t>
   </si>
   <si>
     <t>TwoThreeFive</t>
   </si>
   <si>
-    <t>亮出1次散牌235并且击败1次豹子牌型解锁</t>
+    <t>亮出1次高牌235并战胜豹子解锁</t>
+  </si>
+  <si>
+    <t>11002</t>
   </si>
   <si>
     <t>ShuffleCardAndVictory</t>
   </si>
   <si>
-    <t>使用搓牌并战胜90次敌人解锁</t>
-  </si>
-  <si>
-    <t>180</t>
-  </si>
-  <si>
-    <t>使用180次搓牌后解锁</t>
-  </si>
-  <si>
-    <t>Seven</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>亮出50次数字牌7后解锁</t>
-  </si>
-  <si>
-    <t>Flush</t>
-  </si>
-  <si>
-    <t>亮出20次同花后解锁</t>
+    <t>10</t>
+  </si>
+  <si>
+    <t>使用搓牌并战胜10次敌人解锁</t>
+  </si>
+  <si>
+    <t>11003</t>
+  </si>
+  <si>
+    <t>LuxuryGoods</t>
+  </si>
+  <si>
+    <t>使用[平凡之人]通过难度10,且全程未使用任何技能解锁</t>
+  </si>
+  <si>
+    <t>11004</t>
+  </si>
+  <si>
+    <t>Angel</t>
+  </si>
+  <si>
+    <t>使用[平凡之人]通过难度3解锁</t>
+  </si>
+  <si>
+    <t>11101</t>
+  </si>
+  <si>
+    <t>DeathNum</t>
+  </si>
+  <si>
+    <t>死亡10次后解锁</t>
+  </si>
+  <si>
+    <t>11201</t>
+  </si>
+  <si>
+    <t>CriticalNum</t>
+  </si>
+  <si>
+    <t>触发20次暴击后解锁</t>
+  </si>
+  <si>
+    <t>11301</t>
+  </si>
+  <si>
+    <t>Perspective</t>
+  </si>
+  <si>
+    <t>使用30次透视后解锁</t>
+  </si>
+  <si>
+    <t>11401</t>
   </si>
   <si>
     <t>AccumulateGold</t>
   </si>
   <si>
-    <t>累计获得2000金币后解锁</t>
-  </si>
-  <si>
-    <t>刷新40次商店后解锁</t>
-  </si>
-  <si>
-    <t>击杀150只敌人后解锁</t>
-  </si>
-  <si>
-    <t>亮出35次同花后解锁</t>
-  </si>
-  <si>
-    <t>使用搓牌并战胜200次敌人后解锁</t>
-  </si>
-  <si>
-    <t>亮出60次同花后解锁</t>
-  </si>
-  <si>
-    <t>SingleDamage</t>
-  </si>
-  <si>
-    <t>单次比牌造成300点伤害后解锁</t>
-  </si>
-  <si>
-    <t>亮出60次顺子后解锁</t>
-  </si>
-  <si>
-    <t>使用300次搓牌后解锁</t>
-  </si>
-  <si>
-    <t>ClearDifficulty</t>
-  </si>
-  <si>
-    <t>通关难度3后解锁</t>
-  </si>
-  <si>
-    <t>累计获得5000金币后解锁</t>
+    <t>累计获得10000金币后解锁</t>
+  </si>
+  <si>
+    <t>11501</t>
+  </si>
+  <si>
+    <t>OneDamage</t>
+  </si>
+  <si>
+    <t>2000</t>
+  </si>
+  <si>
+    <t>单次打出2000点伤害后解锁</t>
+  </si>
+  <si>
+    <t>11601</t>
+  </si>
+  <si>
+    <t>NumberOfCoinsOwned</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>拥有1000金币后解锁</t>
   </si>
 </sst>
 </file>
@@ -806,13 +902,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -820,9 +919,24 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1173,429 +1287,560 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.75833333333333" style="2" customWidth="1"/>
-    <col min="2" max="2" width="5.86666666666667" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.3666666666667" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.2166666666667" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="21.4083333333333" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="2" customWidth="1"/>
+    <col min="1" max="1" width="5.75833333333333" style="3" customWidth="1"/>
+    <col min="2" max="2" width="5.86666666666667" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.3666666666667" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.2166666666667" style="3" customWidth="1"/>
+    <col min="5" max="5" width="6.375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="21.4083333333333" style="3" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="B5" s="3">
-        <v>1001</v>
-      </c>
-      <c r="C5" s="2" t="s">
+    <row r="5" s="1" customFormat="1" spans="1:7">
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3">
+      <c r="C5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="6">
         <v>1</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="6">
+        <v>20</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="F6"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:7">
+      <c r="B7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>20</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="F8"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4">
+        <v>20</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" spans="1:7">
+      <c r="B12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8">
         <v>40</v>
       </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="B6" s="3">
-        <v>1002</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="B7" s="3">
-        <v>1003</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="F12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" s="2" customFormat="1" spans="1:7">
+      <c r="C13" s="7"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:7">
+      <c r="B14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:7">
+      <c r="B15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6">
+        <v>3</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" customFormat="1" spans="1:7">
+      <c r="B16" s="3"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="B8" s="3">
-        <v>1004</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
+      <c r="B18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="4">
+        <v>120</v>
+      </c>
+      <c r="F18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="C19" s="3"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="B9" s="3">
-        <v>1005</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="B10" s="3">
-        <v>1006</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="B11" s="3">
-        <v>1007</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="B12" s="3">
-        <v>1008</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:7">
-      <c r="B13" s="4">
-        <v>1009</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="4">
+      <c r="F20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" spans="2:7">
+      <c r="C21" s="4"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="2:7">
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" customFormat="1" spans="2:7">
+      <c r="C23" s="4"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="2:7">
+      <c r="B24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" customFormat="1" spans="2:7">
+      <c r="C25" s="4"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="2:7">
+      <c r="B26" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="2:7">
+      <c r="B28" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28" s="5"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="2:7">
+      <c r="B29" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G29" s="5"/>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="2:7">
+      <c r="B31" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G31" s="5"/>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="2:7">
+      <c r="B33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G33" s="5"/>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="2:7">
+      <c r="B35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G35" s="5"/>
+    </row>
+    <row r="36" customFormat="1" spans="2:7">
+      <c r="C36" s="4"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="2:7">
+      <c r="B37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D37" s="6">
         <v>1</v>
       </c>
-      <c r="E13" s="4">
-        <v>20</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:7">
-      <c r="B14" s="4">
-        <v>1010</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="4">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4">
-        <v>2000</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:7">
-      <c r="B15" s="4">
-        <v>1011</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="4">
-        <v>1</v>
-      </c>
-      <c r="E15" s="4">
-        <v>40</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:7">
-      <c r="B16" s="4">
-        <v>1012</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" s="4">
-        <v>1</v>
-      </c>
-      <c r="E16" s="4">
-        <v>150</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="2:7">
-      <c r="B17" s="4">
-        <v>1013</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4">
-        <v>35</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="2:7">
-      <c r="B18" s="4">
-        <v>1014</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4">
-        <v>100</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="2:7">
-      <c r="B19" s="4">
-        <v>1015</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
-      <c r="E19" s="4">
-        <v>60</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="2:7">
-      <c r="B20" s="4">
-        <v>1016</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="E20" s="4">
-        <v>300</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="2:7">
-      <c r="B21" s="4">
-        <v>1017</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="4">
-        <v>1</v>
-      </c>
-      <c r="E21" s="4">
-        <v>60</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="2:7">
-      <c r="B22" s="4">
-        <v>1018</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4">
-        <v>300</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="2:7">
-      <c r="B23" s="4">
-        <v>1019</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="4">
-        <v>1</v>
-      </c>
-      <c r="E23" s="4">
-        <v>3</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="2:7">
-      <c r="B24" s="4">
-        <v>1020</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="4">
-        <v>5000</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G24" s="5"/>
+      <c r="E37" s="6">
+        <v>10000</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G37" s="5"/>
+    </row>
+    <row r="38" customFormat="1" spans="2:7">
+      <c r="C38" s="4"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="2:7">
+      <c r="B39" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G39" s="5"/>
+    </row>
+    <row r="40" customFormat="1" spans="2:7">
+      <c r="C40" s="4"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="2:7">
+      <c r="B41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" s="5"/>
+    </row>
+    <row r="42" customFormat="1" spans="2:7">
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+    </row>
+    <row r="44" customFormat="1" spans="2:7">
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" customFormat="1" spans="2:7">
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" customFormat="1" spans="2:7">
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" customFormat="1" spans="2:7">
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" customFormat="1" spans="2:7">
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/UnlockConditionConfig.xlsx
+++ b/Config/UnlockConditionConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="13170" windowHeight="10470"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="86">
   <si>
     <t>##var</t>
   </si>
@@ -221,6 +221,15 @@
   </si>
   <si>
     <t>使用[平凡之人]通过难度3解锁</t>
+  </si>
+  <si>
+    <t>11005</t>
+  </si>
+  <si>
+    <t>ThreeCardAttack</t>
+  </si>
+  <si>
+    <t>同时拥有圣物[第一位][第二位][第三位]且成功通过任意难度</t>
   </si>
   <si>
     <t>11101</t>
@@ -446,12 +455,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -778,7 +793,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -802,16 +817,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -820,89 +835,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -912,6 +927,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -919,9 +937,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -937,6 +952,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1287,75 +1305,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="5.75833333333333" style="3" customWidth="1"/>
-    <col min="2" max="2" width="5.86666666666667" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.3666666666667" style="4" customWidth="1"/>
-    <col min="4" max="4" width="10.2166666666667" style="3" customWidth="1"/>
-    <col min="5" max="5" width="6.375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="21.4083333333333" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="3" customWidth="1"/>
+    <col min="1" max="1" width="5.75833333333333" style="4" customWidth="1"/>
+    <col min="2" max="2" width="5.86666666666667" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.3666666666667" style="5" customWidth="1"/>
+    <col min="4" max="4" width="10.2166666666667" style="4" customWidth="1"/>
+    <col min="5" max="5" width="6.375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="21.4083333333333" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1363,7 +1381,7 @@
       <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="6">
@@ -1372,10 +1390,10 @@
       <c r="E5" s="6">
         <v>20</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" spans="1:7">
       <c r="F6"/>
@@ -1402,16 +1420,16 @@
       <c r="F8"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F9" t="s">
@@ -1419,16 +1437,16 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="5">
         <v>1</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="5">
         <v>20</v>
       </c>
       <c r="F11" t="s">
@@ -1436,7 +1454,7 @@
       </c>
     </row>
     <row r="12" s="2" customFormat="1" spans="1:7">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -1464,7 +1482,7 @@
       <c r="B14" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D14" s="6">
@@ -1476,13 +1494,13 @@
       <c r="F14" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="5"/>
+      <c r="G14" s="3"/>
     </row>
     <row r="15" s="1" customFormat="1" spans="1:7">
       <c r="B15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="D15" s="6">
@@ -1494,25 +1512,25 @@
       <c r="F15" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="5"/>
+      <c r="G15" s="3"/>
     </row>
     <row r="16" customFormat="1" spans="1:7">
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
     </row>
     <row r="17" spans="2:7">
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="D17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>37</v>
       </c>
       <c r="F17" t="s">
@@ -1520,16 +1538,16 @@
       </c>
     </row>
     <row r="18" spans="2:7">
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="4">
+      <c r="D18" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="5">
         <v>120</v>
       </c>
       <c r="F18" t="s">
@@ -1537,22 +1555,22 @@
       </c>
     </row>
     <row r="19" spans="2:7">
-      <c r="C19" s="3"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
       <c r="F19"/>
     </row>
     <row r="20" spans="2:7">
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="D20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F20" t="s">
@@ -1560,10 +1578,10 @@
       </c>
     </row>
     <row r="21" customFormat="1" spans="2:7">
-      <c r="C21" s="4"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
     </row>
     <row r="22" s="1" customFormat="1" spans="2:7">
       <c r="B22" s="1" t="s">
@@ -1581,13 +1599,13 @@
       <c r="F22" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G22" s="5"/>
+      <c r="G22" s="3"/>
     </row>
     <row r="23" customFormat="1" spans="2:7">
-      <c r="C23" s="4"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
     </row>
     <row r="24" s="1" customFormat="1" spans="2:7">
       <c r="B24" s="1" t="s">
@@ -1605,25 +1623,25 @@
       <c r="F24" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="G24" s="5"/>
+      <c r="G24" s="3"/>
     </row>
     <row r="25" customFormat="1" spans="2:7">
-      <c r="C25" s="4"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
     </row>
     <row r="26" spans="2:7">
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="3" t="s">
+      <c r="D26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>22</v>
       </c>
       <c r="F26" s="11" t="s">
@@ -1631,16 +1649,16 @@
       </c>
     </row>
     <row r="27" spans="2:7">
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="3" t="s">
+      <c r="D27" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>55</v>
       </c>
       <c r="F27" t="s">
@@ -1663,7 +1681,7 @@
       <c r="F28" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G28" s="5"/>
+      <c r="G28" s="3"/>
     </row>
     <row r="29" s="1" customFormat="1" spans="2:7">
       <c r="B29" s="1" t="s">
@@ -1681,166 +1699,183 @@
       <c r="F29" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="G29" s="5"/>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="2:7">
-      <c r="B31" s="1" t="s">
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" s="3" customFormat="1" spans="2:7">
+      <c r="B30" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C30" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E31" s="1" t="s">
+      <c r="D30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="2:7">
+      <c r="B32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G31" s="5"/>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="2:7">
-      <c r="B33" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="1" t="s">
+      <c r="F32" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="G32" s="3"/>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="2:7">
+      <c r="B34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="G33" s="5"/>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="2:7">
-      <c r="B35" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E35" s="1" t="s">
+      <c r="F34" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="2:7">
+      <c r="B36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="G35" s="5"/>
-    </row>
-    <row r="36" customFormat="1" spans="2:7">
-      <c r="C36" s="4"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="2:7">
-      <c r="B37" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="D37" s="6">
+      <c r="F36" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" customFormat="1" spans="2:7">
+      <c r="C37" s="5"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="2:7">
+      <c r="B38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="6">
         <v>1</v>
       </c>
-      <c r="E37" s="6">
+      <c r="E38" s="6">
         <v>10000</v>
       </c>
-      <c r="F37" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="G37" s="5"/>
-    </row>
-    <row r="38" customFormat="1" spans="2:7">
-      <c r="C38" s="4"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="2:7">
-      <c r="B39" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E39" s="1" t="s">
+      <c r="F38" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F39" s="10" t="s">
+      <c r="G38" s="3"/>
+    </row>
+    <row r="39" customFormat="1" spans="2:7">
+      <c r="C39" s="5"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="2:7">
+      <c r="B40" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G39" s="5"/>
-    </row>
-    <row r="40" customFormat="1" spans="2:7">
-      <c r="C40" s="4"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="2:7">
-      <c r="B41" s="1" t="s">
+      <c r="C40" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="D40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E41" s="1" t="s">
+      <c r="F40" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="G40" s="3"/>
+    </row>
+    <row r="41" customFormat="1" spans="2:7">
+      <c r="C41" s="5"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="2:7">
+      <c r="B42" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G41" s="5"/>
-    </row>
-    <row r="42" customFormat="1" spans="2:7">
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-    </row>
-    <row r="44" customFormat="1" spans="2:7">
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
+      <c r="C42" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="G42" s="3"/>
+    </row>
+    <row r="43" customFormat="1" spans="2:7">
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
     </row>
     <row r="45" customFormat="1" spans="2:7">
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
     </row>
     <row r="46" customFormat="1" spans="2:7">
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
     </row>
     <row r="47" customFormat="1" spans="2:7">
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
     </row>
     <row r="48" customFormat="1" spans="2:7">
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+    </row>
+    <row r="49" customFormat="1" spans="2:5">
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/UnlockConditionConfig.xlsx
+++ b/Config/UnlockConditionConfig.xlsx
@@ -274,10 +274,10 @@
     <t>OneDamage</t>
   </si>
   <si>
-    <t>2000</t>
-  </si>
-  <si>
-    <t>单次打出2000点伤害后解锁</t>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>单次打出10000点伤害后解锁</t>
   </si>
   <si>
     <t>11601</t>
@@ -455,18 +455,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -793,7 +787,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
@@ -817,16 +811,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
@@ -835,89 +829,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -952,9 +946,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1714,7 +1705,7 @@
       <c r="E30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="F30" s="10" t="s">
         <v>65</v>
       </c>
     </row>
